--- a/public/mau-import-cong-viec.xlsx
+++ b/public/mau-import-cong-viec.xlsx
@@ -54,7 +54,7 @@
     <comment ref="F1" authorId="0">
       <text>
         <r>
-          <t>Số nguyên từ 0 đến 100. Không nhập 0,5 để biểu thị 50%.</t>
+          <t>Nhập nội dung tiến độ thực hiện. Có thể để trống.</t>
         </r>
       </text>
     </comment>
@@ -178,15 +178,17 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,7 +537,7 @@
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
     <col min="5" max="5" width="18" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40" style="2" customWidth="1"/>
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
@@ -575,12 +577,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" errorTitle="Tiến độ không hợp lệ" error="Nhập số nguyên từ 0 đến 100." sqref="F2:F501">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>

--- a/public/mau-import-cong-viec.xlsx
+++ b/public/mau-import-cong-viec.xlsx
@@ -86,12 +86,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <t>Tên hoặc mã dự án có trong hệ thống. Khách hàng tự lấy theo dự án.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <t>Nội dung cần thực hiện; có thể để trống.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Công việc</t>
   </si>
@@ -121,6 +135,12 @@
   </si>
   <si>
     <t>KPI</t>
+  </si>
+  <si>
+    <t>Dự án</t>
+  </si>
+  <si>
+    <t>Mô tả công việc</t>
   </si>
 </sst>
 </file>
@@ -529,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -541,9 +561,11 @@
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -574,9 +596,15 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
